--- a/table/Datas/#Queue.xlsx
+++ b/table/Datas/#Queue.xlsx
@@ -546,21 +546,11 @@
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -666,7 +656,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">

--- a/table/Datas/#Queue.xlsx
+++ b/table/Datas/#Queue.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,11 @@
           <t>max_wait_seconds</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ticket_ttl_seconds</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -539,6 +544,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -551,6 +561,11 @@
           <t>c</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -611,6 +626,11 @@
       <c r="L4" t="inlineStr">
         <is>
           <t>max_wait_seconds</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ticket_ttl_seconds</t>
         </is>
       </c>
     </row>
@@ -658,6 +678,9 @@
       <c r="L5" t="n">
         <v>10</v>
       </c>
+      <c r="M5" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -702,6 +725,9 @@
       </c>
       <c r="L6" t="n">
         <v>60</v>
+      </c>
+      <c r="M6" t="n">
+        <v>600</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#Queue.xlsx
+++ b/table/Datas/#Queue.xlsx
@@ -672,7 +672,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1,2,3,4,5</t>
+          <t>1,2,3,4,5,6</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -720,7 +720,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1,2,3,4,5</t>
+          <t>1,2,3,4,5,6</t>
         </is>
       </c>
       <c r="L6" t="n">

--- a/table/Datas/#Queue.xlsx
+++ b/table/Datas/#Queue.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -672,7 +672,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6</t>
+          <t>1,2,3,4,5,6,7</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -720,7 +720,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6</t>
+          <t>1,2,3,4,5,6,7</t>
         </is>
       </c>
       <c r="L6" t="n">

--- a/table/Datas/#Queue.xlsx
+++ b/table/Datas/#Queue.xlsx
@@ -672,7 +672,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7</t>
+          <t>1,2,3,4,5,6,7,8</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -720,7 +720,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7</t>
+          <t>1,2,3,4,5,6,7,8</t>
         </is>
       </c>
       <c r="L6" t="n">
